--- a/app/public/templates/machine-inventory-template.xlsx
+++ b/app/public/templates/machine-inventory-template.xlsx
@@ -9777,7 +9777,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the dropdown list." promptTitle="Tip" prompt="Pick the machine type. See the &quot;Machine types&quot; sheet for the 3D twin of each." type="list">
-      <formula1>=Lists!$A$1:$A$17</formula1>
+      <formula1>=Lists!$A$1:$A$31</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the dropdown list." type="list">
       <formula1>=Lists!$B$1:$B$3</formula1>
@@ -9793,7 +9793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cnc-mill</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>No 3D twin yet</t>
+          <t>Same machine type</t>
         </is>
       </c>
     </row>
@@ -9934,12 +9934,12 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>cnc-mill</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>No 3D twin yet</t>
+          <t>Closest twin (similar controls and hazards)</t>
         </is>
       </c>
     </row>
@@ -10291,6 +10291,384 @@
       <c r="E18" s="6" t="inlineStr">
         <is>
           <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Industrial lockstitch sewing machine</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>ماكينة خياطة صناعية غرزة مقفولة</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Garments</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>lockstitch</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Same machine type</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Overlock / coverstitch machine</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>ماكينة أوفرلوك / كافر ستيتش</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Garments</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>lockstitch</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Closest twin (similar controls and hazards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Straight-knife / band-knife cutter</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>ماكينة قص بالسكين</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Garments</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Fusing press</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>مكبس لصق حراري</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Garments</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Pump and motor alignment rig</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>منصة محاذاة مضخة ومحرك</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Industrial maintenance</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>pump-rig</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Same machine type</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Gearbox / drive train rig</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>منصة علبة تروس ونقل حركة</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Industrial maintenance</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>pump-rig</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Closest twin (similar controls and hazards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Hydraulic / pneumatic trainer</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>وحدة تدريب هيدروليك وهوائيات</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Industrial maintenance</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Mechatronic production line</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>خط إنتاج ميكاتروني</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Industrial maintenance</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Sheetfed offset press</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>ماكينة طباعة أوفست بالأفرخ</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Printing</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>offset-press</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Same machine type</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Flexo label press</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>ماكينة طباعة فلكسو للملصقات</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Printing</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>offset-press</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Closest twin (similar controls and hazards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Guillotine paper cutter</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>مقصلة ورق</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Printing</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Digital / wide-format printer</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>طابعة رقمية أو عريضة النسق</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Printing</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Vision inspection cell</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>خلية فحص بالرؤية الآلية</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>AI for technicians</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>vision-cell</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Same machine type</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Edge AI and IoT sensor kit</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>طقم ذكاء اصطناعي طرفي وحساسات</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>AI for technicians</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>vision-cell</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>Closest twin (similar controls and hazards)</t>
         </is>
       </c>
     </row>
@@ -10305,7 +10683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10442,6 +10820,104 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Industrial lockstitch sewing machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Overlock / coverstitch machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Straight-knife / band-knife cutter</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fusing press</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Pump and motor alignment rig</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Gearbox / drive train rig</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Hydraulic / pneumatic trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mechatronic production line</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sheetfed offset press</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Flexo label press</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Guillotine paper cutter</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Digital / wide-format printer</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Vision inspection cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Edge AI and IoT sensor kit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/app/public/templates/machine-inventory-template.xlsx
+++ b/app/public/templates/machine-inventory-template.xlsx
@@ -9777,7 +9777,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="G2:G501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the dropdown list." promptTitle="Tip" prompt="Pick the machine type. See the &quot;Machine types&quot; sheet for the 3D twin of each." type="list">
-      <formula1>=Lists!$A$1:$A$31</formula1>
+      <formula1>=Lists!$A$1:$A$49</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Pick from the list" error="Choose a value from the dropdown list." type="list">
       <formula1>=Lists!$B$1:$B$3</formula1>
@@ -9793,7 +9793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10672,6 +10672,492 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Electronics bench (scope, generator, supply, rework)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>طاولة إلكترونيات (راسم موجات ومولد ومصدر ولحام)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Industrial electronics</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>electronics-bench</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Same machine type</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>PLC and process-control trainer</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>وحدة تدريب PLC والتحكم في العمليات</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Industrial electronics</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>electronics-bench</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Closest twin (similar controls and hazards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>PCB exposure and etching line</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>خط تعريض وحفر الدوائر المطبوعة</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Industrial electronics</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Network rack (switch, router, server, UPS)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>خزانة شبكات (سويتش وموجه وخادم وUPS)</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Computer systems &amp; networks</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>network-rack</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Same machine type</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>PC assembly bench</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>طاولة تجميع حاسبات</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Computer systems &amp; networks</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>network-rack</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>Closest twin (similar controls and hazards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Split air-conditioner service rig</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>منصة صيانة مكيف سبليت</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Refrigeration &amp; AC</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>split-ac</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>Same machine type</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Domestic refrigeration trainer</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>وحدة تدريب التبريد المنزلي</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Refrigeration &amp; AC</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>split-ac</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>Closest twin (similar controls and hazards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Refrigerant recovery machine</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>ماكينة استرجاع وسيط التبريد</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Refrigeration &amp; AC</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Washing machine on repair bench</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>غسالة على طاولة الإصلاح</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Home appliances</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>washing-machine</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Same machine type</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Dishwasher trainer</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>وحدة تدريب غسالة أطباق</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Home appliances</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>washing-machine</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Closest twin (similar controls and hazards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Appliance safety tester (PAT)</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>جهاز اختبار سلامة الأجهزة</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Home appliances</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Laser multifunction printer (MFP)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>طابعة ليزر متعددة الوظائف</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Office equipment</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>laser-mfp</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>Same machine type</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Photocopier</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>ماكينة تصوير مستندات</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Office equipment</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>laser-mfp</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Closest twin (similar controls and hazards)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>POS terminal and banknote counter</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>جهاز نقاط بيع وعداد نقود</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Office equipment</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>TV / display repair bench</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>طاولة إصلاح التلفزيون والشاشات</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Audio-visual electronics</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>tv-bench</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Same machine type</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>IP-CCTV kit with NVR</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>طقم كاميرات IP مع جهاز تسجيل</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Audio-visual electronics</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>No 3D twin yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Motor rewinding and test bench</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>طاولة لف واختبار المحركات</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Industrial electricity &amp; machines</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>motor-rewind</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>Same machine type</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Motor-control bench (DOL, star-delta, VFD)</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>طاولة التحكم في المحركات</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Industrial electricity &amp; machines</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>dol-panel</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>Closest twin (similar controls and hazards)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10683,7 +11169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10918,6 +11404,132 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Electronics bench (scope, generator, supply, rework)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PLC and process-control trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PCB exposure and etching line</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Network rack (switch, router, server, UPS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PC assembly bench</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Split air-conditioner service rig</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Domestic refrigeration trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Refrigerant recovery machine</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Washing machine on repair bench</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Dishwasher trainer</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Appliance safety tester (PAT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Laser multifunction printer (MFP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Photocopier</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>POS terminal and banknote counter</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TV / display repair bench</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>IP-CCTV kit with NVR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Motor rewinding and test bench</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Motor-control bench (DOL, star-delta, VFD)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
